--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.17891690405007</v>
+        <v>10.26657399690814</v>
       </c>
       <c r="D2" t="n">
-        <v>32.18388042833208</v>
+        <v>5.229880569603964</v>
       </c>
       <c r="E2" t="n">
-        <v>12.85930782438597</v>
+        <v>2.08963752146272</v>
       </c>
       <c r="F2" t="n">
-        <v>16.00850509099537</v>
+        <v>2.601382077286748</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.98935120367545</v>
+        <v>4.385769570597261</v>
       </c>
       <c r="D3" t="n">
-        <v>27.4832969919057</v>
+        <v>4.466035761184677</v>
       </c>
       <c r="E3" t="n">
-        <v>12.85930782438597</v>
+        <v>2.08963752146272</v>
       </c>
       <c r="F3" t="n">
-        <v>16.00850509099537</v>
+        <v>2.601382077286748</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.25396435817852</v>
+        <v>3.941269208204011</v>
       </c>
       <c r="D4" t="n">
-        <v>24.47431203214173</v>
+        <v>3.97707570522303</v>
       </c>
       <c r="E4" t="n">
-        <v>12.85930782438597</v>
+        <v>2.08963752146272</v>
       </c>
       <c r="F4" t="n">
-        <v>16.00850509099537</v>
+        <v>2.601382077286748</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>45.11772230578065</v>
+        <v>7.331629874689355</v>
       </c>
       <c r="D5" t="n">
-        <v>45.19110550682539</v>
+        <v>7.343554644859127</v>
       </c>
       <c r="E5" t="n">
-        <v>12.85930782438597</v>
+        <v>2.08963752146272</v>
       </c>
       <c r="F5" t="n">
-        <v>16.00850509099537</v>
+        <v>2.601382077286748</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.59326868617084</v>
+        <v>6.758906161502763</v>
       </c>
       <c r="D6" t="n">
-        <v>61.45413863990289</v>
+        <v>9.986297528984219</v>
       </c>
       <c r="E6" t="n">
-        <v>12.85930782438597</v>
+        <v>2.08963752146272</v>
       </c>
       <c r="F6" t="n">
-        <v>16.00850509099537</v>
+        <v>2.601382077286748</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.55312559424583</v>
+        <v>7.077382909064947</v>
       </c>
       <c r="D7" t="n">
-        <v>65.18124857700118</v>
+        <v>10.59195289376269</v>
       </c>
       <c r="E7" t="n">
-        <v>12.85930782438597</v>
+        <v>2.08963752146272</v>
       </c>
       <c r="F7" t="n">
-        <v>16.00850509099537</v>
+        <v>2.601382077286748</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
